--- a/data/trans_orig/IP1010-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP1010-Habitat-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3469</t>
+          <t>2459</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3981</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>599</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5067</t>
+          <t>5608</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>135257</t>
+          <t>136267</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>149096</t>
+          <t>149116</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>286736</t>
+          <t>286195</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>291202</t>
+          <t>291204</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3218</t>
+          <t>3697</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3341</t>
+          <t>3340</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4586</t>
+          <t>3947</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>191945</t>
+          <t>191466</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>208801</t>
+          <t>208802</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>402719</t>
+          <t>403358</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>640</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5386</t>
+          <t>5583</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>641</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5471</t>
+          <t>5420</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>144271</t>
+          <t>144074</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>149015</t>
+          <t>149017</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>282003</t>
+          <t>282054</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>286832</t>
+          <t>286833</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3526</t>
+          <t>3955</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4208</t>
+          <t>3921</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>204298</t>
+          <t>203869</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>412931</t>
+          <t>413218</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4323</t>
+          <t>4360</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9275</t>
+          <t>9933</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>2718</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10560</t>
+          <t>10625</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>676698</t>
+          <t>676661</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>713425</t>
+          <t>712767</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>720686</t>
+          <t>720693</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1393161</t>
+          <t>1393096</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1401086</t>
+          <t>1401003</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5767</t>
+          <t>6233</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3452</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>686</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6417</t>
+          <t>6821</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>130624</t>
+          <t>130158</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>149646</t>
+          <t>148997</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>283072</t>
+          <t>282668</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>288801</t>
+          <t>288803</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2256</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2646</t>
+          <t>2478</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>152583</t>
+          <t>152802</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>318178</t>
+          <t>318346</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>623</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>5315</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>623</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5891</t>
+          <t>5335</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>201897</t>
+          <t>201767</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>207082</t>
+          <t>206459</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>411491</t>
+          <t>412047</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>416758</t>
+          <t>416759</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>443</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5962</t>
+          <t>6428</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>686</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6731</t>
+          <t>6345</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9159</t>
+          <t>9590</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>700966</t>
+          <t>700500</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>706928</t>
+          <t>706485</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>741411</t>
+          <t>741797</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>747454</t>
+          <t>747456</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1445911</t>
+          <t>1445480</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1453079</t>
+          <t>1453105</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>719</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7163</t>
+          <t>6570</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>726</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6644</t>
+          <t>7280</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>140913</t>
+          <t>141506</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>147346</t>
+          <t>147357</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>275139</t>
+          <t>274503</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>281054</t>
+          <t>281057</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4646</t>
+          <t>4600</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4547</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>219713</t>
+          <t>219759</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>427059</t>
+          <t>427427</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2644</t>
+          <t>2985</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>3066</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>153353</t>
+          <t>153012</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>320060</t>
+          <t>319604</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4486</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>4108</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -5803,7 +5803,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>201250</t>
+          <t>201624</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>409045</t>
+          <t>409048</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2983</t>
+          <t>2598</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2171</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10137</t>
+          <t>10557</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2643</t>
+          <t>2558</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10800</t>
+          <t>10088</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>701388</t>
+          <t>701773</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>734707</t>
+          <t>734287</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>742665</t>
+          <t>742673</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1438415</t>
+          <t>1439127</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1446572</t>
+          <t>1446657</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">

--- a/data/trans_orig/IP1010-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP1010-Habitat-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1275</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4469</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>605</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2459</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3441</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,44%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1275</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3961</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>600</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5608</t>
+          <t>5019</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>151802</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>148608</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,17%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>97,08%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>202</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>138121</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>136267</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>135285</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,56%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>98,23%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>97,52%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>151802</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>149116</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,17%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>97,41%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>426</t>
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>286195</t>
+          <t>286784</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>291204</t>
+          <t>291203</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1070,102 +1070,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3195</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3697</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3499</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1309</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3340</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4606</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1309</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3947</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>211475</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>208947</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,69%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,49%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>311</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>194521</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>191466</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>191664</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,67%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,11%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,21%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>211475</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>208802</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,69%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,43%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>632</t>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>403358</t>
+          <t>402699</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>312</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,84 +1408,84 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6144</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,11%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>2015</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>640</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5583</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>3,73%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
           <t>641</t>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5420</t>
+          <t>5810</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -1526,69 +1526,69 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>147642</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>143513</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>149015</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,65%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,89%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,57%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>147642</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>144074</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>149017</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,65%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>96,27%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,57%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>458</t>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>282054</t>
+          <t>281664</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,107 +1751,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3517</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>700</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3955</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3534</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3921</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>207124</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>204307</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,66%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,31%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>207124</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>203869</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,66%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,1%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>579</t>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>413218</t>
+          <t>413605</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,74 +2094,74 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4658</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>9829</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>1247</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4360</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4377</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,18%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>0,64%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>4658</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>9933</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>9</t>
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2718</t>
+          <t>2702</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10625</t>
+          <t>10642</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2207,74 +2207,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1079</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>718042</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>712871</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>720694</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,36%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>98,64%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,72%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>679774</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>676661</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>676644</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,82%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>99,36%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1079</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>718042</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>712767</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>720693</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,36%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>98,63%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,72%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2095</t>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1393096</t>
+          <t>1393079</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1401003</t>
+          <t>1401019</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3509</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1652</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6233</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5954</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,21%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,57%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4101</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>689</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6821</t>
+          <t>6701</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -2782,74 +2782,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>152411</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>149589</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,55%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>97,71%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>134739</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>130158</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>130437</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>136391</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,79%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>95,43%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>95,63%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>152411</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>148997</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,55%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>97,32%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>391</t>
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>282668</t>
+          <t>282788</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>288803</t>
+          <t>288800</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3125,47 +3125,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>317</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>205398</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>317</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3355,107 +3355,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>443</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2037</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2181</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>2211</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>443</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>2478</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -3468,74 +3468,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>154396</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>152802</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>152658</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>154839</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,71%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>98,68%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>98,59%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>495</t>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>318346</t>
+          <t>318613</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,92 +3698,92 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1962</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5182</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1962</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>623</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5315</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,57%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1962</t>
-        </is>
-      </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>622</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3811,74 +3811,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>205120</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>201900</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>206459</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,05%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,5%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,7%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>278</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>205120</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>201767</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>206459</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,05%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>97,43%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,7%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>553</t>
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>412047</t>
+          <t>412059</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>416759</t>
+          <t>416760</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2649</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6022</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>2095</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>443</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>6428</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>7101</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,3%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,06%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>686</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>6345</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1965</t>
+          <t>1772</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9590</t>
+          <t>9189</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -4154,74 +4154,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>745493</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>742120</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>747492</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,65%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,2%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,91%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1015</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>704833</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>700500</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>699827</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>706485</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,7%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,09%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>99,0%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>99,94%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1062</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>745493</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>741797</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>747456</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,65%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>99,15%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,91%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2077</t>
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1445480</t>
+          <t>1445881</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1453105</t>
+          <t>1453298</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,88%</t>
         </is>
       </c>
     </row>
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4616,84 +4616,84 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2905</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>730</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7150</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,96%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4,83%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>2905</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6570</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,96%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>4,44%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2905</t>
-        </is>
-      </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
           <t>726</t>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7280</t>
+          <t>7169</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -4729,74 +4729,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>145171</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>140926</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>147346</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,04%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>95,17%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,51%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>145171</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>141506</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>147357</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,04%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>95,56%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>99,51%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>378</t>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>274503</t>
+          <t>274614</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4959,107 +4959,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1334</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4736</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,11%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>1334</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4600</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4017</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,05%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1334</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4179</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -5072,74 +5072,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>223025</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>219623</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,41%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,89%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>334</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>330</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>223025</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>219759</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,41%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>97,95%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>664</t>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>427427</t>
+          <t>427589</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>334</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5302,107 +5302,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>524</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2985</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2617</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,91%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3394</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3066</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -5415,74 +5415,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>155473</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>153012</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>153380</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,66%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>98,09%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>98,32%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>506</t>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>319604</t>
+          <t>319276</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5645,107 +5645,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4638</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>818</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4112</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3294</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>818</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4108</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -5758,74 +5758,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>204918</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>201098</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,6%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,75%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>281</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>204918</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>201624</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,6%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>570</t>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>409048</t>
+          <t>409862</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>281</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5057</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2192</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>10311</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>524</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2598</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3127</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,07%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>5057</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2171</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>10557</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2558</t>
+          <t>2663</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10088</t>
+          <t>11001</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -6101,74 +6101,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1058</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>739787</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>734533</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>742652</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,32%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>98,62%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,71%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1060</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>703847</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>701773</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>701244</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,93%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>99,56%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1058</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>739787</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>734287</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>742673</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,32%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>98,58%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2118</t>
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1439127</t>
+          <t>1438214</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1446657</t>
+          <t>1446552</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
